--- a/펨트론/펨트론 추가개발 요구사항_250618.xlsx
+++ b/펨트론/펨트론 추가개발 요구사항_250618.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joyang\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://seksystemco-my.sharepoint.com/personal/mnkim_ksystem_co_kr/Documents/PC Migration_20240731/ODC 추가개발 프로젝트/펨트론/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB8D76A-90D8-4E4A-849F-B6B561429786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{7CB8D76A-90D8-4E4A-849F-B6B561429786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2698FEC1-DF39-4EF6-9399-65B69D915281}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{CB6E75FF-42CE-4E71-8B55-1E5FD6DAD603}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="85">
   <si>
     <t>모듈</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -405,6 +405,14 @@
   <si>
     <t>프로젝트 구매발주 이후 입고된 품목들에 대한 자재출고처리 및 기타출고처리를 매번 입력하고 있는데,
 구매발주한 이후 각 프로젝트로 자재출고 및 기타출고처리가 자동으로 처리될 수 있는 기능 개선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">수정 테스트 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -458,7 +466,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -481,13 +489,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -511,6 +530,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1228,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B03E8F30-9666-4351-9FB1-172FCACEE3F7}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.796875" style="1"/>
@@ -1239,7 +1264,7 @@
     <col min="6" max="6" width="50.69921875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -1258,8 +1283,11 @@
       <c r="F1" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="G1" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1273,7 +1301,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1287,7 +1315,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1301,7 +1329,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1314,8 +1342,11 @@
       <c r="E5" s="6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="G5" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1329,7 +1360,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1343,7 +1374,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1357,7 +1388,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1371,7 +1402,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1385,7 +1416,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1399,7 +1430,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1413,7 +1444,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1427,7 +1458,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1438,7 +1469,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1452,7 +1483,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>15</v>
       </c>
